--- a/data/rugvista_trends_monthly.xlsx
+++ b/data/rugvista_trends_monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -561,7 +561,7 @@
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -641,7 +641,7 @@
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -761,7 +761,7 @@
         <v>43585</v>
       </c>
       <c r="B41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -785,7 +785,7 @@
         <v>43677</v>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
@@ -793,7 +793,7 @@
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46">
@@ -801,7 +801,7 @@
         <v>43738</v>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47">
@@ -817,7 +817,7 @@
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -825,7 +825,7 @@
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
@@ -849,7 +849,7 @@
         <v>43921</v>
       </c>
       <c r="B52" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
@@ -905,7 +905,7 @@
         <v>44135</v>
       </c>
       <c r="B59" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60">
@@ -937,7 +937,7 @@
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
@@ -961,7 +961,7 @@
         <v>44347</v>
       </c>
       <c r="B66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
@@ -993,7 +993,7 @@
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
@@ -1033,7 +1033,7 @@
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76">
@@ -1081,7 +1081,7 @@
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
@@ -1105,7 +1105,7 @@
         <v>44895</v>
       </c>
       <c r="B84" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
@@ -1121,7 +1121,7 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87">
@@ -1145,7 +1145,7 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90">
@@ -1201,7 +1201,7 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97">
@@ -1225,7 +1225,7 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="100">
@@ -1233,7 +1233,7 @@
         <v>45382</v>
       </c>
       <c r="B100" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101">
@@ -1249,7 +1249,7 @@
         <v>45443</v>
       </c>
       <c r="B102" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103">
@@ -1297,7 +1297,7 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109">
@@ -1305,7 +1305,7 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110">
@@ -1313,7 +1313,7 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111">
@@ -1345,7 +1345,7 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115">
@@ -1353,7 +1353,7 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="116">
@@ -1385,7 +1385,7 @@
         <v>45961</v>
       </c>
       <c r="B119" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="120">
@@ -1409,7 +1409,23 @@
         <v>46053</v>
       </c>
       <c r="B122" t="n">
-        <v>72</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B123" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B124" t="n">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/data/rugvista_trends_monthly.xlsx
+++ b/data/rugvista_trends_monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,7 +457,7 @@
         <v>42429</v>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         <v>42490</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         <v>42582</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         <v>42613</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -537,7 +537,7 @@
         <v>42735</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -561,7 +561,7 @@
         <v>42825</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -617,7 +617,7 @@
         <v>43039</v>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -633,7 +633,7 @@
         <v>43100</v>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -641,7 +641,7 @@
         <v>43131</v>
       </c>
       <c r="B26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -657,7 +657,7 @@
         <v>43190</v>
       </c>
       <c r="B28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -665,7 +665,7 @@
         <v>43220</v>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
@@ -681,7 +681,7 @@
         <v>43281</v>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
@@ -689,7 +689,7 @@
         <v>43312</v>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -713,7 +713,7 @@
         <v>43404</v>
       </c>
       <c r="B35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
@@ -745,7 +745,7 @@
         <v>43524</v>
       </c>
       <c r="B39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -753,7 +753,7 @@
         <v>43555</v>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -761,7 +761,7 @@
         <v>43585</v>
       </c>
       <c r="B41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42">
@@ -785,7 +785,7 @@
         <v>43677</v>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -793,7 +793,7 @@
         <v>43708</v>
       </c>
       <c r="B45" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
@@ -809,7 +809,7 @@
         <v>43769</v>
       </c>
       <c r="B47" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -817,7 +817,7 @@
         <v>43799</v>
       </c>
       <c r="B48" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
@@ -825,7 +825,7 @@
         <v>43830</v>
       </c>
       <c r="B49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -849,7 +849,7 @@
         <v>43921</v>
       </c>
       <c r="B52" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
@@ -865,7 +865,7 @@
         <v>43982</v>
       </c>
       <c r="B54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
@@ -889,7 +889,7 @@
         <v>44074</v>
       </c>
       <c r="B57" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
@@ -897,7 +897,7 @@
         <v>44104</v>
       </c>
       <c r="B58" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
@@ -905,7 +905,7 @@
         <v>44135</v>
       </c>
       <c r="B59" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60">
@@ -913,7 +913,7 @@
         <v>44165</v>
       </c>
       <c r="B60" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
@@ -921,7 +921,7 @@
         <v>44196</v>
       </c>
       <c r="B61" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62">
@@ -929,7 +929,7 @@
         <v>44227</v>
       </c>
       <c r="B62" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
@@ -937,7 +937,7 @@
         <v>44255</v>
       </c>
       <c r="B63" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
@@ -945,7 +945,7 @@
         <v>44286</v>
       </c>
       <c r="B64" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="65">
@@ -953,7 +953,7 @@
         <v>44316</v>
       </c>
       <c r="B65" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66">
@@ -969,7 +969,7 @@
         <v>44377</v>
       </c>
       <c r="B67" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
@@ -985,7 +985,7 @@
         <v>44439</v>
       </c>
       <c r="B69" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
@@ -993,7 +993,7 @@
         <v>44469</v>
       </c>
       <c r="B70" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
@@ -1009,7 +1009,7 @@
         <v>44530</v>
       </c>
       <c r="B72" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73">
@@ -1017,7 +1017,7 @@
         <v>44561</v>
       </c>
       <c r="B73" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74">
@@ -1025,7 +1025,7 @@
         <v>44592</v>
       </c>
       <c r="B74" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75">
@@ -1033,7 +1033,7 @@
         <v>44620</v>
       </c>
       <c r="B75" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76">
@@ -1041,7 +1041,7 @@
         <v>44651</v>
       </c>
       <c r="B76" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
@@ -1057,7 +1057,7 @@
         <v>44712</v>
       </c>
       <c r="B78" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
@@ -1065,7 +1065,7 @@
         <v>44742</v>
       </c>
       <c r="B79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80">
@@ -1073,7 +1073,7 @@
         <v>44773</v>
       </c>
       <c r="B80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81">
@@ -1081,7 +1081,7 @@
         <v>44804</v>
       </c>
       <c r="B81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82">
@@ -1097,7 +1097,7 @@
         <v>44865</v>
       </c>
       <c r="B83" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
@@ -1105,7 +1105,7 @@
         <v>44895</v>
       </c>
       <c r="B84" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85">
@@ -1113,7 +1113,7 @@
         <v>44926</v>
       </c>
       <c r="B85" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86">
@@ -1121,7 +1121,7 @@
         <v>44957</v>
       </c>
       <c r="B86" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87">
@@ -1137,7 +1137,7 @@
         <v>45016</v>
       </c>
       <c r="B88" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89">
@@ -1145,7 +1145,7 @@
         <v>45046</v>
       </c>
       <c r="B89" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
@@ -1153,7 +1153,7 @@
         <v>45077</v>
       </c>
       <c r="B90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91">
@@ -1161,7 +1161,7 @@
         <v>45107</v>
       </c>
       <c r="B91" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -1169,7 +1169,7 @@
         <v>45138</v>
       </c>
       <c r="B92" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93">
@@ -1177,7 +1177,7 @@
         <v>45169</v>
       </c>
       <c r="B93" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
@@ -1185,7 +1185,7 @@
         <v>45199</v>
       </c>
       <c r="B94" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95">
@@ -1193,7 +1193,7 @@
         <v>45230</v>
       </c>
       <c r="B95" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96">
@@ -1201,7 +1201,7 @@
         <v>45260</v>
       </c>
       <c r="B96" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97">
@@ -1209,7 +1209,7 @@
         <v>45291</v>
       </c>
       <c r="B97" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98">
@@ -1217,7 +1217,7 @@
         <v>45322</v>
       </c>
       <c r="B98" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="99">
@@ -1225,7 +1225,7 @@
         <v>45351</v>
       </c>
       <c r="B99" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="100">
@@ -1241,7 +1241,7 @@
         <v>45412</v>
       </c>
       <c r="B101" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102">
@@ -1257,7 +1257,7 @@
         <v>45473</v>
       </c>
       <c r="B103" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104">
@@ -1265,7 +1265,7 @@
         <v>45504</v>
       </c>
       <c r="B104" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105">
@@ -1273,7 +1273,7 @@
         <v>45535</v>
       </c>
       <c r="B105" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106">
@@ -1281,7 +1281,7 @@
         <v>45565</v>
       </c>
       <c r="B106" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107">
@@ -1289,7 +1289,7 @@
         <v>45596</v>
       </c>
       <c r="B107" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="108">
@@ -1297,7 +1297,7 @@
         <v>45626</v>
       </c>
       <c r="B108" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109">
@@ -1305,7 +1305,7 @@
         <v>45657</v>
       </c>
       <c r="B109" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110">
@@ -1313,7 +1313,7 @@
         <v>45688</v>
       </c>
       <c r="B110" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="111">
@@ -1321,7 +1321,7 @@
         <v>45716</v>
       </c>
       <c r="B111" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="112">
@@ -1329,7 +1329,7 @@
         <v>45747</v>
       </c>
       <c r="B112" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="113">
@@ -1337,7 +1337,7 @@
         <v>45777</v>
       </c>
       <c r="B113" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114">
@@ -1345,7 +1345,7 @@
         <v>45808</v>
       </c>
       <c r="B114" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115">
@@ -1353,7 +1353,7 @@
         <v>45838</v>
       </c>
       <c r="B115" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116">
@@ -1361,7 +1361,7 @@
         <v>45869</v>
       </c>
       <c r="B116" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="117">
@@ -1369,7 +1369,7 @@
         <v>45900</v>
       </c>
       <c r="B117" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118">
@@ -1377,7 +1377,7 @@
         <v>45930</v>
       </c>
       <c r="B118" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="119">
@@ -1417,7 +1417,7 @@
         <v>46081</v>
       </c>
       <c r="B123" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124">
@@ -1425,7 +1425,15 @@
         <v>46112</v>
       </c>
       <c r="B124" t="n">
-        <v>73</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B125" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/rugvista_trends_monthly.xlsx
+++ b/data/rugvista_trends_monthly.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,994 +446,1010 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>42400</v>
+        <v>42369</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>42429</v>
+        <v>42400</v>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>42460</v>
+        <v>42429</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>42490</v>
+        <v>42460</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>42521</v>
+        <v>42490</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>42551</v>
+        <v>42521</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>42582</v>
+        <v>42551</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>42613</v>
+        <v>42582</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>42643</v>
+        <v>42613</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>42674</v>
+        <v>42643</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>42704</v>
+        <v>42674</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>42735</v>
+        <v>42704</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>42766</v>
+        <v>42735</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>42794</v>
+        <v>42766</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>42825</v>
+        <v>42794</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>42855</v>
+        <v>42825</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>59.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>42886</v>
+        <v>42855</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>42916</v>
+        <v>42886</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>42947</v>
+        <v>42916</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>42978</v>
+        <v>42947</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>43008</v>
+        <v>42978</v>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>43039</v>
+        <v>43008</v>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>43069</v>
+        <v>43039</v>
       </c>
       <c r="B24" t="n">
-        <v>20</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>43100</v>
+        <v>43069</v>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>43131</v>
+        <v>43100</v>
       </c>
       <c r="B26" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>43159</v>
+        <v>43131</v>
       </c>
       <c r="B27" t="n">
-        <v>17</v>
+        <v>79.60997634917221</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>43190</v>
+        <v>43159</v>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>73.56697484411954</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>43220</v>
+        <v>43190</v>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>62.0064502257579</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>43251</v>
+        <v>43220</v>
       </c>
       <c r="B30" t="n">
-        <v>10</v>
+        <v>51.28669103418619</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>43281</v>
+        <v>43251</v>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>40.98731455600946</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>43312</v>
+        <v>43281</v>
       </c>
       <c r="B32" t="n">
-        <v>14</v>
+        <v>48.08127284454956</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>43343</v>
+        <v>43312</v>
       </c>
       <c r="B33" t="n">
-        <v>15</v>
+        <v>56.12109223822834</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>43373</v>
+        <v>43343</v>
       </c>
       <c r="B34" t="n">
-        <v>18</v>
+        <v>72.77875725650398</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>43404</v>
+        <v>43373</v>
       </c>
       <c r="B35" t="n">
-        <v>18</v>
+        <v>77.35041926467426</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>43434</v>
+        <v>43404</v>
       </c>
       <c r="B36" t="n">
-        <v>20</v>
+        <v>85.91571705009676</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>43465</v>
+        <v>43434</v>
       </c>
       <c r="B37" t="n">
-        <v>15</v>
+        <v>94.58611051386798</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>43496</v>
+        <v>43465</v>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>70.83448720705225</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>43524</v>
+        <v>43496</v>
       </c>
       <c r="B39" t="n">
-        <v>20</v>
+        <v>87.49215222532789</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>43555</v>
+        <v>43524</v>
       </c>
       <c r="B40" t="n">
-        <v>16</v>
+        <v>85.91571705009676</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>43585</v>
+        <v>43555</v>
       </c>
       <c r="B41" t="n">
-        <v>17</v>
+        <v>75.24850569769941</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>43616</v>
+        <v>43585</v>
       </c>
       <c r="B42" t="n">
-        <v>15</v>
+        <v>72.51601806063212</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>43646</v>
+        <v>43616</v>
       </c>
       <c r="B43" t="n">
-        <v>13</v>
+        <v>69.36314771016986</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>43677</v>
+        <v>43646</v>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>58.85357987529564</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>43708</v>
+        <v>43677</v>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>63.05740700924532</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>43738</v>
+        <v>43708</v>
       </c>
       <c r="B46" t="n">
-        <v>19</v>
+        <v>81.97462911201892</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>43769</v>
+        <v>43738</v>
       </c>
       <c r="B47" t="n">
-        <v>22</v>
+        <v>88.9109438830359</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>43799</v>
+        <v>43769</v>
       </c>
       <c r="B48" t="n">
-        <v>31</v>
+        <v>97.45683968345948</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>43830</v>
+        <v>43799</v>
       </c>
       <c r="B49" t="n">
-        <v>20</v>
+        <v>141.6585757147553</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>43861</v>
+        <v>43830</v>
       </c>
       <c r="B50" t="n">
-        <v>25</v>
+        <v>90.32065579406955</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>43890</v>
+        <v>43861</v>
       </c>
       <c r="B51" t="n">
-        <v>23</v>
+        <v>113.4333707791086</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>43921</v>
+        <v>43890</v>
       </c>
       <c r="B52" t="n">
-        <v>18</v>
+        <v>103.3149010851975</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>43951</v>
+        <v>43921</v>
       </c>
       <c r="B53" t="n">
-        <v>22</v>
+        <v>82.65192086815797</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>43982</v>
+        <v>43951</v>
       </c>
       <c r="B54" t="n">
-        <v>26</v>
+        <v>102.2497990121542</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>44012</v>
+        <v>43982</v>
       </c>
       <c r="B55" t="n">
-        <v>21</v>
+        <v>118.0133096931946</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>44043</v>
+        <v>44012</v>
       </c>
       <c r="B56" t="n">
-        <v>22</v>
+        <v>96.3917376104162</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>44074</v>
+        <v>44043</v>
       </c>
       <c r="B57" t="n">
-        <v>24</v>
+        <v>103.8474521217191</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>44104</v>
+        <v>44074</v>
       </c>
       <c r="B58" t="n">
-        <v>29</v>
+        <v>108.2143706211965</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>44135</v>
+        <v>44104</v>
       </c>
       <c r="B59" t="n">
-        <v>37</v>
+        <v>132.6052080938875</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>44165</v>
+        <v>44135</v>
       </c>
       <c r="B60" t="n">
-        <v>41</v>
+        <v>167.2210254677939</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>44196</v>
+        <v>44165</v>
       </c>
       <c r="B61" t="n">
-        <v>33</v>
+        <v>176.8069441251833</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>44227</v>
+        <v>44196</v>
       </c>
       <c r="B62" t="n">
-        <v>46</v>
+        <v>154.9723516277962</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>44255</v>
+        <v>44227</v>
       </c>
       <c r="B63" t="n">
-        <v>35</v>
+        <v>191.7183731477891</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>44286</v>
+        <v>44255</v>
       </c>
       <c r="B64" t="n">
-        <v>36</v>
+        <v>154.9723516277962</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>44316</v>
+        <v>44286</v>
       </c>
       <c r="B65" t="n">
-        <v>29</v>
+        <v>150.1793922991015</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>44347</v>
+        <v>44316</v>
       </c>
       <c r="B66" t="n">
-        <v>24</v>
+        <v>127.2796977286711</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>44377</v>
+        <v>44347</v>
       </c>
       <c r="B67" t="n">
-        <v>19</v>
+        <v>102.6758398413715</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>44408</v>
+        <v>44377</v>
       </c>
       <c r="B68" t="n">
-        <v>20</v>
+        <v>81.48030858781038</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>44439</v>
+        <v>44408</v>
       </c>
       <c r="B69" t="n">
-        <v>25</v>
+        <v>99.79671261380231</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>44469</v>
+        <v>44439</v>
       </c>
       <c r="B70" t="n">
-        <v>25</v>
+        <v>119.7560551365628</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>44500</v>
+        <v>44469</v>
       </c>
       <c r="B71" t="n">
-        <v>30</v>
+        <v>121.4193336801261</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>44530</v>
+        <v>44500</v>
       </c>
       <c r="B72" t="n">
-        <v>38</v>
+        <v>145.9249708886265</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>44561</v>
+        <v>44530</v>
       </c>
       <c r="B73" t="n">
-        <v>25</v>
+        <v>172.4265423494029</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>44592</v>
+        <v>44561</v>
       </c>
       <c r="B74" t="n">
-        <v>41</v>
+        <v>126.9635954920041</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>44620</v>
+        <v>44592</v>
       </c>
       <c r="B75" t="n">
-        <v>32</v>
+        <v>186.2871968790976</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>44651</v>
+        <v>44620</v>
       </c>
       <c r="B76" t="n">
-        <v>31</v>
+        <v>151.9127736454546</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>44681</v>
+        <v>44651</v>
       </c>
       <c r="B77" t="n">
-        <v>25</v>
+        <v>141.9331023840744</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>44712</v>
+        <v>44681</v>
       </c>
       <c r="B78" t="n">
-        <v>23</v>
+        <v>120.8649074989384</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>44742</v>
+        <v>44712</v>
       </c>
       <c r="B79" t="n">
-        <v>19</v>
+        <v>101.5708763936032</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>44773</v>
+        <v>44742</v>
       </c>
       <c r="B80" t="n">
-        <v>20</v>
+        <v>90.37146753360987</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>44804</v>
+        <v>44773</v>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>93.58713938449907</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>44834</v>
+        <v>44804</v>
       </c>
       <c r="B82" t="n">
-        <v>24</v>
+        <v>101.4599911573657</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>44865</v>
+        <v>44834</v>
       </c>
       <c r="B83" t="n">
-        <v>28</v>
+        <v>119.7560551365628</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>44895</v>
+        <v>44865</v>
       </c>
       <c r="B84" t="n">
-        <v>34</v>
+        <v>134.8364472648707</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>44926</v>
+        <v>44895</v>
       </c>
       <c r="B85" t="n">
-        <v>28</v>
+        <v>166.882280537525</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>44957</v>
+        <v>44926</v>
       </c>
       <c r="B86" t="n">
-        <v>35</v>
+        <v>130.2901525791308</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>44985</v>
+        <v>44957</v>
       </c>
       <c r="B87" t="n">
-        <v>35</v>
+        <v>168.9891000260386</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45016</v>
+        <v>44985</v>
       </c>
       <c r="B88" t="n">
-        <v>31</v>
+        <v>159.1203140008959</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45046</v>
+        <v>45016</v>
       </c>
       <c r="B89" t="n">
-        <v>27</v>
+        <v>146.3685118335767</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45077</v>
+        <v>45046</v>
       </c>
       <c r="B90" t="n">
-        <v>24</v>
+        <v>131.7422440567146</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45107</v>
+        <v>45077</v>
       </c>
       <c r="B91" t="n">
-        <v>22</v>
+        <v>110.1282821411598</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45138</v>
+        <v>45107</v>
       </c>
       <c r="B92" t="n">
-        <v>27</v>
+        <v>101.8943918876152</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45169</v>
+        <v>45138</v>
       </c>
       <c r="B93" t="n">
-        <v>33</v>
+        <v>130.9188550313601</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45199</v>
+        <v>45169</v>
       </c>
       <c r="B94" t="n">
-        <v>34</v>
+        <v>150.2684971271901</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45230</v>
+        <v>45199</v>
       </c>
       <c r="B95" t="n">
-        <v>46</v>
+        <v>159.5316236624278</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45260</v>
+        <v>45230</v>
       </c>
       <c r="B96" t="n">
-        <v>58</v>
+        <v>213.2577575668067</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45291</v>
+        <v>45260</v>
       </c>
       <c r="B97" t="n">
-        <v>42</v>
+        <v>276.8645597754393</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45322</v>
+        <v>45291</v>
       </c>
       <c r="B98" t="n">
-        <v>47</v>
+        <v>192.6730319329451</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45351</v>
+        <v>45322</v>
       </c>
       <c r="B99" t="n">
-        <v>44</v>
+        <v>222.3150368457059</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45382</v>
+        <v>45351</v>
       </c>
       <c r="B100" t="n">
-        <v>40</v>
+        <v>199.671838648458</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45412</v>
+        <v>45382</v>
       </c>
       <c r="B101" t="n">
-        <v>34</v>
+        <v>190.2028648568817</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45443</v>
+        <v>45412</v>
       </c>
       <c r="B102" t="n">
-        <v>29</v>
+        <v>165.7070413525863</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45473</v>
+        <v>45443</v>
       </c>
       <c r="B103" t="n">
-        <v>32</v>
+        <v>141.0053705919523</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45504</v>
+        <v>45473</v>
       </c>
       <c r="B104" t="n">
-        <v>32</v>
+        <v>149.0334135891584</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45535</v>
+        <v>45504</v>
       </c>
       <c r="B105" t="n">
-        <v>39</v>
+        <v>151.2977334088831</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45565</v>
+        <v>45535</v>
       </c>
       <c r="B106" t="n">
-        <v>48</v>
+        <v>183.2040581413687</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45596</v>
+        <v>45565</v>
       </c>
       <c r="B107" t="n">
-        <v>64</v>
+        <v>228.9021490485416</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45626</v>
+        <v>45596</v>
       </c>
       <c r="B108" t="n">
-        <v>87</v>
+        <v>308.7708845079248</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45657</v>
+        <v>45626</v>
       </c>
       <c r="B109" t="n">
-        <v>60</v>
+        <v>384.9343693532129</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45688</v>
+        <v>45657</v>
       </c>
       <c r="B110" t="n">
-        <v>70</v>
+        <v>284.8926027726453</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45716</v>
+        <v>45688</v>
       </c>
       <c r="B111" t="n">
-        <v>60</v>
+        <v>311.3896862791095</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45747</v>
+        <v>45716</v>
       </c>
       <c r="B112" t="n">
-        <v>62</v>
+        <v>280.2507176511986</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45777</v>
+        <v>45747</v>
       </c>
       <c r="B113" t="n">
-        <v>52</v>
+        <v>274.0229239256164</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45808</v>
+        <v>45777</v>
       </c>
       <c r="B114" t="n">
-        <v>48</v>
+        <v>228.3524366046803</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45838</v>
+        <v>45808</v>
       </c>
       <c r="B115" t="n">
-        <v>38</v>
+        <v>214.5128949922754</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45869</v>
+        <v>45838</v>
       </c>
       <c r="B116" t="n">
-        <v>46</v>
+        <v>177.1461326387823</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="B117" t="n">
-        <v>59</v>
+        <v>223.739256067212</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45930</v>
+        <v>45900</v>
       </c>
       <c r="B118" t="n">
-        <v>64</v>
+        <v>271.2550156031354</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45961</v>
+        <v>45930</v>
       </c>
       <c r="B119" t="n">
-        <v>78</v>
+        <v>287.170488457401</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>45991</v>
+        <v>45961</v>
       </c>
       <c r="B120" t="n">
-        <v>100</v>
+        <v>369.0544429974631</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46022</v>
+        <v>45991</v>
       </c>
       <c r="B121" t="n">
-        <v>66</v>
+        <v>428.1031538770573</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="B122" t="n">
-        <v>74</v>
+        <v>299.8567349354388</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46081</v>
+        <v>46053</v>
       </c>
       <c r="B123" t="n">
-        <v>72</v>
+        <v>340.2220646382863</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46112</v>
+        <v>46081</v>
       </c>
       <c r="B124" t="n">
-        <v>72</v>
+        <v>313.6962765478437</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B125" t="n">
+        <v>331.2263625902232</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B125" t="n">
-        <v>40</v>
+      <c r="B126" t="n">
+        <v>254.878224695123</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B127" t="n">
+        <v>242.653296270832</v>
       </c>
     </row>
   </sheetData>

--- a/data/rugvista_trends_monthly.xlsx
+++ b/data/rugvista_trends_monthly.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -429,1027 +417,1035 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Rugvista</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B3" t="n">
-        <v>50.8</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B4" t="n">
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B8" t="n">
-        <v>34.25</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B9" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B10" t="n">
-        <v>40.25</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B11" t="n">
-        <v>51.25</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B12" t="n">
-        <v>65.40000000000001</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B13" t="n">
-        <v>60.75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B14" t="n">
-        <v>50.5</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B15" t="n">
-        <v>61.4</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B16" t="n">
-        <v>59.25</v>
+        <v>62.25</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B17" t="n">
-        <v>59.25</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B18" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B19" t="n">
-        <v>42.75</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B20" t="n">
-        <v>47</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B21" t="n">
-        <v>58</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B22" t="n">
-        <v>67.25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B23" t="n">
-        <v>67.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B24" t="n">
-        <v>85.40000000000001</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B25" t="n">
-        <v>89</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B26" t="n">
-        <v>70</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B27" t="n">
-        <v>79.60997634917221</v>
+        <v>84.30521631132271</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B28" t="n">
-        <v>73.56697484411954</v>
+        <v>76.57079279652247</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B29" t="n">
-        <v>62.0064502257579</v>
+        <v>61.87538811840199</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B30" t="n">
-        <v>51.28669103418619</v>
+        <v>55.06909542537777</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B31" t="n">
-        <v>40.98731455600946</v>
+        <v>40.21900227696129</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B32" t="n">
-        <v>48.08127284454956</v>
+        <v>48.21123990892155</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B33" t="n">
-        <v>56.12109223822834</v>
+        <v>59.1941212999379</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B34" t="n">
-        <v>72.77875725650398</v>
+        <v>71.6723245704823</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B35" t="n">
-        <v>77.35041926467426</v>
+        <v>81.46926102256262</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B36" t="n">
-        <v>85.91571705009676</v>
+        <v>86.36772924860279</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B37" t="n">
-        <v>94.58611051386798</v>
+        <v>92.55526806044298</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B38" t="n">
-        <v>70.83448720705225</v>
+        <v>75.48797350445044</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B39" t="n">
-        <v>87.49215222532789</v>
+        <v>92.55526806044298</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B40" t="n">
-        <v>85.91571705009676</v>
+        <v>88.68805630304286</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B41" t="n">
-        <v>75.24850569769941</v>
+        <v>74.6629683295384</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B42" t="n">
-        <v>72.51601806063212</v>
+        <v>72.44576692196233</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B43" t="n">
-        <v>69.36314771016986</v>
+        <v>68.83636928172221</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B44" t="n">
-        <v>58.85357987529564</v>
+        <v>56.51285448147382</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B45" t="n">
-        <v>63.05740700924532</v>
+        <v>64.96915752432209</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B46" t="n">
-        <v>81.97462911201892</v>
+        <v>85.33647277996275</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B47" t="n">
-        <v>88.9109438830359</v>
+        <v>87.86305112813083</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B48" t="n">
-        <v>97.45683968345948</v>
+        <v>101.1109123227474</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B49" t="n">
-        <v>141.6585757147553</v>
+        <v>143.2855174627169</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B50" t="n">
-        <v>90.32065579406955</v>
+        <v>92.56785128157408</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B51" t="n">
-        <v>113.4333707791086</v>
+        <v>116.7912142337617</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B52" t="n">
-        <v>103.3149010851975</v>
+        <v>106.5179129817178</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B53" t="n">
-        <v>82.65192086815797</v>
+        <v>84.78177033265665</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B54" t="n">
-        <v>102.2497990121542</v>
+        <v>104.3551127181297</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B55" t="n">
-        <v>118.0133096931946</v>
+        <v>115.9260941283264</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B56" t="n">
-        <v>96.3917376104162</v>
+        <v>95.70391166377695</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B57" t="n">
-        <v>103.8474521217191</v>
+        <v>103.8144126522326</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B58" t="n">
-        <v>108.2143706211965</v>
+        <v>109.4376933375619</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B59" t="n">
-        <v>132.6052080938875</v>
+        <v>134.6343164083642</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B60" t="n">
-        <v>167.2210254677939</v>
+        <v>168.698420559878</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B61" t="n">
-        <v>176.8069441251833</v>
+        <v>181.6752221414071</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B62" t="n">
-        <v>154.9723516277962</v>
+        <v>154.6402188465548</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B63" t="n">
-        <v>191.7183731477891</v>
+        <v>194.2194636702185</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B64" t="n">
-        <v>154.9723516277962</v>
+        <v>155.7216189783489</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B65" t="n">
-        <v>150.1793922991015</v>
+        <v>154.0995187806578</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B66" t="n">
-        <v>127.2796977286711</v>
+        <v>132.471516144776</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B67" t="n">
-        <v>102.6758398413715</v>
+        <v>105.1120928103855</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B68" t="n">
-        <v>81.48030858781038</v>
+        <v>81.64570995045378</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B69" t="n">
-        <v>99.79671261380231</v>
+        <v>99.68354603426008</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B70" t="n">
-        <v>119.7560551365628</v>
+        <v>120.0682711783447</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B71" t="n">
-        <v>121.4193336801261</v>
+        <v>122.6443628174323</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B72" t="n">
-        <v>145.9249708886265</v>
+        <v>144.7091477261393</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B73" t="n">
-        <v>172.4265423494029</v>
+        <v>173.606175677644</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B74" t="n">
-        <v>126.9635954920041</v>
+        <v>127.6845421112994</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B75" t="n">
-        <v>186.2871968790976</v>
+        <v>182.7905023909128</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B76" t="n">
-        <v>151.9127736454546</v>
+        <v>155.125518266798</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B77" t="n">
-        <v>141.9331023840744</v>
+        <v>143.3650999144415</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B78" t="n">
-        <v>120.8649074989384</v>
+        <v>119.2842432881876</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B79" t="n">
-        <v>101.5708763936032</v>
+        <v>103.4916815007374</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B80" t="n">
-        <v>90.37146753360987</v>
+        <v>89.60318744652591</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B81" t="n">
-        <v>93.58713938449907</v>
+        <v>91.84326713268906</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B82" t="n">
-        <v>101.4599911573657</v>
+        <v>99.68354603426008</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B83" t="n">
-        <v>119.7560551365628</v>
+        <v>120.96430305281</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B84" t="n">
-        <v>134.8364472648707</v>
+        <v>137.0928767931846</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B85" t="n">
-        <v>166.882280537525</v>
+        <v>167.4459565406953</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B86" t="n">
-        <v>130.2901525791308</v>
+        <v>130.4846417190033</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B87" t="n">
-        <v>168.9891000260386</v>
+        <v>171.1420880228645</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B88" t="n">
-        <v>159.1203140008959</v>
+        <v>162.965797168369</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B89" t="n">
-        <v>146.3685118335767</v>
+        <v>147.285239365227</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B90" t="n">
-        <v>131.7422440567146</v>
+        <v>134.4412084488215</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B91" t="n">
-        <v>110.1282821411598</v>
+        <v>111.6798013222014</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B92" t="n">
-        <v>101.8943918876152</v>
+        <v>103.1708640786051</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B93" t="n">
-        <v>130.9188550313601</v>
+        <v>132.7394210001022</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B94" t="n">
-        <v>150.2684971271901</v>
+        <v>148.9064017629352</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B95" t="n">
-        <v>159.5316236624278</v>
+        <v>160.6061904728801</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B96" t="n">
-        <v>213.2577575668067</v>
+        <v>214.4252185386267</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B97" t="n">
-        <v>276.8645597754393</v>
+        <v>278.6676947277787</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B98" t="n">
-        <v>192.6730319329451</v>
+        <v>198.2582377757937</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B99" t="n">
-        <v>222.3150368457059</v>
+        <v>226.5504541107514</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B100" t="n">
-        <v>199.671838648458</v>
+        <v>205.2781110017607</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B101" t="n">
-        <v>190.2028648568817</v>
+        <v>189.7493005321974</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B102" t="n">
-        <v>165.7070413525863</v>
+        <v>161.6698076283296</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B103" t="n">
-        <v>141.0053705919523</v>
+        <v>142.524698830238</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B104" t="n">
-        <v>149.0334135891584</v>
+        <v>148.9064017629352</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B105" t="n">
-        <v>151.2977334088831</v>
+        <v>153.1608703847333</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B106" t="n">
-        <v>183.2040581413687</v>
+        <v>189.3238536700176</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B107" t="n">
-        <v>228.9021490485416</v>
+        <v>230.5921993014597</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B108" t="n">
-        <v>308.7708845079248</v>
+        <v>308.4489750803658</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B109" t="n">
-        <v>384.9343693532129</v>
+        <v>392.4747303608792</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B110" t="n">
-        <v>284.8926027726453</v>
+        <v>287.6020788335548</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B111" t="n">
-        <v>311.3896862791095</v>
+        <v>313.925352624057</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B112" t="n">
-        <v>280.2507176511986</v>
+        <v>284.263114580839</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B113" t="n">
-        <v>274.0229239256164</v>
+        <v>276.8475550700346</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B114" t="n">
-        <v>228.3524366046803</v>
+        <v>229.8823448349394</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B115" t="n">
-        <v>214.5128949922754</v>
+        <v>218.7590055687326</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B116" t="n">
-        <v>177.1461326387823</v>
+        <v>180.9396520636297</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B117" t="n">
-        <v>223.739256067212</v>
+        <v>226.1745650795372</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B118" t="n">
-        <v>271.2550156031354</v>
+        <v>271.9038487294982</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B119" t="n">
-        <v>287.170488457401</v>
+        <v>291.6786740916435</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B120" t="n">
-        <v>369.0544429974631</v>
+        <v>372.0139021253589</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B121" t="n">
-        <v>428.1031538770573</v>
+        <v>438.0123817715189</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B122" t="n">
-        <v>299.8567349354388</v>
+        <v>299.0942336024481</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B123" t="n">
-        <v>340.2220646382863</v>
+        <v>339.8798109118728</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B124" t="n">
-        <v>313.6962765478437</v>
+        <v>322.5768387199956</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>331.2263625902232</v>
+        <v>332.2170660840414</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B126" t="n">
-        <v>254.878224695123</v>
+        <v>257.0727297078892</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="B127" t="n">
-        <v>242.653296270832</v>
+        <v>244.2190932224948</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B128" t="n">
+        <v>218.7590055687326</v>
       </c>
     </row>
   </sheetData>

--- a/data/rugvista_trends_monthly.xlsx
+++ b/data/rugvista_trends_monthly.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,47 +429,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Rugvista</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B2" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B5" t="n">
@@ -465,987 +477,1003 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B6" t="n">
-        <v>27.75</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B7" t="n">
-        <v>27.2</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B8" t="n">
-        <v>35.5</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B10" t="n">
-        <v>38.75</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B11" t="n">
-        <v>56.75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B12" t="n">
-        <v>67.2</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B14" t="n">
-        <v>54.25</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B15" t="n">
-        <v>64.2</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B16" t="n">
-        <v>62.25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B17" t="n">
-        <v>56</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B18" t="n">
-        <v>53.8</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B19" t="n">
-        <v>44.25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B20" t="n">
-        <v>45.75</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B21" t="n">
-        <v>55.2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B22" t="n">
-        <v>69</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B23" t="n">
-        <v>65</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B24" t="n">
-        <v>88</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B25" t="n">
-        <v>91.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B26" t="n">
-        <v>69.59999999999999</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B27" t="n">
-        <v>84.30521631132271</v>
+        <v>82.50679851668727</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B28" t="n">
-        <v>76.57079279652247</v>
+        <v>73.45117428924598</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B29" t="n">
-        <v>61.87538811840199</v>
+        <v>62.13164400494438</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B30" t="n">
-        <v>55.06909542537777</v>
+        <v>52.7238566131026</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B31" t="n">
-        <v>40.21900227696129</v>
+        <v>40.49876390605686</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B32" t="n">
-        <v>48.21123990892155</v>
+        <v>46.78739184177998</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B33" t="n">
-        <v>59.1941212999379</v>
+        <v>56.14487021013597</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B34" t="n">
-        <v>71.6723245704823</v>
+        <v>71.43881334981458</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B35" t="n">
-        <v>81.46926102256262</v>
+        <v>79.89072929542645</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B36" t="n">
-        <v>86.36772924860279</v>
+        <v>87.28615574783684</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B37" t="n">
-        <v>92.55526806044298</v>
+        <v>89.80160692212608</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B38" t="n">
-        <v>75.48797350445044</v>
+        <v>71.84128553770087</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B39" t="n">
-        <v>92.55526806044298</v>
+        <v>90.55624227441285</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B40" t="n">
-        <v>88.68805630304286</v>
+        <v>86.02843016069221</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B41" t="n">
-        <v>74.6629683295384</v>
+        <v>75.26229913473423</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B42" t="n">
-        <v>72.44576692196233</v>
+        <v>74.7088998763906</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B43" t="n">
-        <v>68.83636928172221</v>
+        <v>68.92336217552534</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B44" t="n">
-        <v>56.51285448147382</v>
+        <v>56.54734239802225</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B45" t="n">
-        <v>64.96915752432209</v>
+        <v>65.90482076637825</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B46" t="n">
-        <v>85.33647277996275</v>
+        <v>80.49443757725587</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B47" t="n">
-        <v>87.86305112813083</v>
+        <v>86.73275648949321</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B48" t="n">
-        <v>101.1109123227474</v>
+        <v>100.8411100658088</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B49" t="n">
-        <v>143.2855174627169</v>
+        <v>139.5853260384616</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B50" t="n">
-        <v>92.56785128157408</v>
+        <v>92.98611833436681</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B51" t="n">
-        <v>116.7912142337617</v>
+        <v>114.109677179731</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B52" t="n">
-        <v>106.5179129817178</v>
+        <v>105.6177942268208</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B53" t="n">
-        <v>84.78177033265665</v>
+        <v>84.0696412338111</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B54" t="n">
-        <v>104.3551127181297</v>
+        <v>101.9025954349225</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B55" t="n">
-        <v>115.9260941283264</v>
+        <v>114.2158257166423</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B56" t="n">
-        <v>95.70391166377695</v>
+        <v>93.41071248201233</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B57" t="n">
-        <v>103.8144126522326</v>
+        <v>101.3718527503656</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B58" t="n">
-        <v>109.4376933375619</v>
+        <v>107.4223193543142</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B59" t="n">
-        <v>134.6343164083642</v>
+        <v>129.5012150318807</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B60" t="n">
-        <v>168.698420559878</v>
+        <v>163.4687468435216</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B61" t="n">
-        <v>181.6752221414071</v>
+        <v>176.6311654205324</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B62" t="n">
-        <v>154.6402188465548</v>
+        <v>152.8538931523838</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B63" t="n">
-        <v>194.2194636702185</v>
+        <v>189.7935839975432</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B64" t="n">
-        <v>155.7216189783489</v>
+        <v>154.4461212060545</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B65" t="n">
-        <v>154.0995187806578</v>
+        <v>150.2001797295994</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B66" t="n">
-        <v>132.471516144776</v>
+        <v>128.439729662767</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B67" t="n">
-        <v>105.1120928103855</v>
+        <v>105.2993486160866</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B68" t="n">
-        <v>81.64570995045378</v>
+        <v>82.26511610631768</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B69" t="n">
-        <v>99.68354603426008</v>
+        <v>98.86154228309408</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B70" t="n">
-        <v>120.0682711783447</v>
+        <v>120.8554584314678</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B71" t="n">
-        <v>122.6443628174323</v>
+        <v>122.1884230465208</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B72" t="n">
-        <v>144.7091477261393</v>
+        <v>141.7385707339641</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B73" t="n">
-        <v>173.606175677644</v>
+        <v>172.1745961110065</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B74" t="n">
-        <v>127.6845421112994</v>
+        <v>124.4100307382757</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B75" t="n">
-        <v>182.7905023909128</v>
+        <v>185.2820814923606</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B76" t="n">
-        <v>155.125518266798</v>
+        <v>151.0693230393348</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B77" t="n">
-        <v>143.3650999144415</v>
+        <v>143.8490980411313</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B78" t="n">
-        <v>119.2842432881876</v>
+        <v>118.3006095859497</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B79" t="n">
-        <v>103.4916815007374</v>
+        <v>102.6382753590775</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B80" t="n">
-        <v>89.60318744652591</v>
+        <v>87.19810190138074</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B81" t="n">
-        <v>91.84326713268906</v>
+        <v>92.41887997700481</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B82" t="n">
-        <v>99.68354603426008</v>
+        <v>98.30614036015535</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B83" t="n">
-        <v>120.96430305281</v>
+        <v>119.4114134318271</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B84" t="n">
-        <v>137.0928767931846</v>
+        <v>134.6294261203483</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B85" t="n">
-        <v>167.4459565406953</v>
+        <v>166.0651749586805</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B86" t="n">
-        <v>130.4846417190033</v>
+        <v>129.4086480447243</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B87" t="n">
-        <v>171.1420880228645</v>
+        <v>167.5092199583212</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B88" t="n">
-        <v>162.965797168369</v>
+        <v>156.6233422687221</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B89" t="n">
-        <v>147.285239365227</v>
+        <v>147.7369115017024</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B90" t="n">
-        <v>134.4412084488215</v>
+        <v>136.1925174285711</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B91" t="n">
-        <v>111.6798013222014</v>
+        <v>110.7086414680103</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B92" t="n">
-        <v>103.1708640786051</v>
+        <v>103.3976934465379</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B93" t="n">
-        <v>132.7394210001022</v>
+        <v>130.3437590113932</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B94" t="n">
-        <v>148.9064017629352</v>
+        <v>148.3078027212968</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B95" t="n">
-        <v>160.6061904728801</v>
+        <v>161.8852776183169</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B96" t="n">
-        <v>214.4252185386267</v>
+        <v>214.7329876021029</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B97" t="n">
-        <v>278.6676947277787</v>
+        <v>276.7716036700256</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B98" t="n">
-        <v>198.2582377757937</v>
+        <v>195.5156385170898</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B99" t="n">
-        <v>226.5504541107514</v>
+        <v>221.4172829360205</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B100" t="n">
-        <v>205.2781110017607</v>
+        <v>206.7953868930758</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B101" t="n">
-        <v>189.7493005321974</v>
+        <v>185.4891955162134</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B102" t="n">
-        <v>161.6698076283296</v>
+        <v>160.8408564723923</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B103" t="n">
-        <v>142.524698830238</v>
+        <v>139.9524335538998</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B104" t="n">
-        <v>148.9064017629352</v>
+        <v>148.7255711796666</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B105" t="n">
-        <v>153.1608703847333</v>
+        <v>154.5743295968445</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B106" t="n">
-        <v>189.3238536700176</v>
+        <v>183.818121682734</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B107" t="n">
-        <v>230.5921993014597</v>
+        <v>228.9371151866778</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B108" t="n">
-        <v>308.4489750803658</v>
+        <v>306.0153957559152</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B109" t="n">
-        <v>392.4747303608792</v>
+        <v>388.5246662839605</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B110" t="n">
-        <v>287.6020788335548</v>
+        <v>283.2470147747583</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B111" t="n">
-        <v>313.925352624057</v>
+        <v>314.5723461054329</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B112" t="n">
-        <v>284.263114580839</v>
+        <v>281.2646859295636</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B113" t="n">
-        <v>276.8475550700346</v>
+        <v>272.3826432159984</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B114" t="n">
-        <v>229.8823448349394</v>
+        <v>225.7519189697813</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B115" t="n">
-        <v>218.7590055687326</v>
+        <v>218.350216708477</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B116" t="n">
-        <v>180.9396520636297</v>
+        <v>176.6539606364627</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B117" t="n">
-        <v>226.1745650795372</v>
+        <v>222.0510678391291</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B118" t="n">
-        <v>271.9038487294982</v>
+        <v>268.4350686766361</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B119" t="n">
-        <v>291.6786740916435</v>
+        <v>287.4327711473172</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B120" t="n">
-        <v>372.0139021253589</v>
+        <v>367.6178789781138</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B121" t="n">
-        <v>438.0123817715189</v>
+        <v>433.2463056950119</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B122" t="n">
-        <v>299.0942336024481</v>
+        <v>293.6008563650707</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B123" t="n">
-        <v>339.8798109118728</v>
+        <v>340.478304019998</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B124" t="n">
-        <v>322.5768387199956</v>
+        <v>314.5723461054329</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B125" t="n">
-        <v>332.2170660840414</v>
+        <v>330.6093676715923</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B126" t="n">
-        <v>257.0727297078892</v>
+        <v>255.3587280149985</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B127" t="n">
-        <v>244.2190932224948</v>
+        <v>243.7627278056218</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B128" t="n">
-        <v>218.7590055687326</v>
+        <v>229.4527701004334</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B129" t="n">
+        <v>262.7604302763028</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B130" t="n">
+        <v>304.9501331657373</v>
       </c>
     </row>
   </sheetData>
